--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdulaziz\Desktop\Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FCFD02A-7876-44F0-930E-A90ADD84E347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AE2A21-EF30-45A3-8957-18ED33DA849E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,14 +158,6 @@
     </font>
     <font>
       <b/>
-      <sz val="48"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -183,6 +175,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -192,7 +192,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -210,30 +210,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -273,32 +249,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -307,14 +276,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -621,11 +591,11 @@
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" style="7" customWidth="1"/>
-    <col min="4" max="5" width="8.7265625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" style="12" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" style="5" customWidth="1"/>
+    <col min="4" max="5" width="8.7265625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.36328125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" style="9" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -636,7 +606,7 @@
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -645,583 +615,630 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="14">
+    <row r="2" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="8">
         <v>1</v>
       </c>
-      <c r="E2" s="3">
-        <v>2</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="8">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="11" t="str">
+      <c r="G2" s="8" t="str">
         <f t="array" ref="G2">_xlfn.IFS(AND(D2="", E2=""), "Have not started", OR(D2="", E2=""), "...", TRUE, "Finished")</f>
         <v>Finished</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" s="15"/>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="D3" s="8">
+        <v>1</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="11" t="str">
+      <c r="G3" s="8" t="str">
         <f t="array" ref="G3">_xlfn.IFS(AND(D3="", E3=""), "Have not started", OR(D3="", E3=""), "...", TRUE, "Finished")</f>
         <v>Finished</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="15"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="11">
+        <v>1</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="3">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3">
-        <v>4</v>
-      </c>
-      <c r="F4" s="4" t="s">
+      <c r="D4" s="8">
+        <v>1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="11" t="str">
+      <c r="G4" s="8" t="str">
         <f t="array" ref="G4">_xlfn.IFS(AND(D4="", E4=""), "Have not started", OR(D4="", E4=""), "...", TRUE, "Finished")</f>
         <v>Finished</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="15"/>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="11">
+        <v>1</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="8">
+        <v>0</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="11" t="str">
+      <c r="G5" s="8" t="str">
         <f t="array" ref="G5">_xlfn.IFS(AND(D5="", E5=""), "Have not started", OR(D5="", E5=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" s="15"/>
-      <c r="B6" s="9" t="s">
+        <v>Finished</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="4" t="s">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="11" t="str">
+      <c r="G6" s="8" t="str">
         <f t="array" ref="G6">_xlfn.IFS(AND(D6="", E6=""), "Have not started", OR(D6="", E6=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A7" s="16"/>
-      <c r="B7" s="9" t="s">
+    <row r="7" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="11">
+        <v>1</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4" t="s">
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="11" t="str">
+      <c r="G7" s="8" t="str">
         <f t="array" ref="G7">_xlfn.IFS(AND(D7="", E7=""), "Have not started", OR(D7="", E7=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A8" s="14">
+    <row r="8" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="11">
         <v>2</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4" t="s">
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="11" t="str">
+      <c r="G8" s="8" t="str">
         <f t="array" ref="G8">_xlfn.IFS(AND(D8="", E8=""), "Have not started", OR(D8="", E8=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="15"/>
-      <c r="B9" s="9" t="s">
+    <row r="9" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="11">
+        <v>2</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="4" t="s">
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="11" t="str">
+      <c r="G9" s="8" t="str">
         <f t="array" ref="G9">_xlfn.IFS(AND(D9="", E9=""), "Have not started", OR(D9="", E9=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="15"/>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11">
+        <v>2</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="4" t="s">
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G10" s="11" t="str">
+      <c r="G10" s="8" t="str">
         <f t="array" ref="G10">_xlfn.IFS(AND(D10="", E10=""), "Have not started", OR(D10="", E10=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A11" s="15"/>
-      <c r="B11" s="9" t="s">
+    <row r="11" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="11">
+        <v>2</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4" t="s">
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="11" t="str">
+      <c r="G11" s="8" t="str">
         <f t="array" ref="G11">_xlfn.IFS(AND(D11="", E11=""), "Have not started", OR(D11="", E11=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A12" s="15"/>
-      <c r="B12" s="9" t="s">
+    <row r="12" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="11">
+        <v>2</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4" t="s">
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="11" t="str">
+      <c r="G12" s="8" t="str">
         <f t="array" ref="G12">_xlfn.IFS(AND(D12="", E12=""), "Have not started", OR(D12="", E12=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="16"/>
-      <c r="B13" s="9" t="s">
+    <row r="13" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="11">
+        <v>2</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4" t="s">
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G13" s="11" t="str">
+      <c r="G13" s="8" t="str">
         <f t="array" ref="G13">_xlfn.IFS(AND(D13="", E13=""), "Have not started", OR(D13="", E13=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A14" s="14">
+    <row r="14" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="11">
         <v>3</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="4" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="11" t="str">
+      <c r="G14" s="8" t="str">
         <f t="array" ref="G14">_xlfn.IFS(AND(D14="", E14=""), "Have not started", OR(D14="", E14=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A15" s="15"/>
-      <c r="B15" s="9" t="s">
+    <row r="15" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="11">
+        <v>3</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="11" t="str">
+      <c r="G15" s="8" t="str">
         <f t="array" ref="G15">_xlfn.IFS(AND(D15="", E15=""), "Have not started", OR(D15="", E15=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A16" s="15"/>
-      <c r="B16" s="9" t="s">
+    <row r="16" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="11">
+        <v>3</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4" t="s">
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="11" t="str">
+      <c r="G16" s="8" t="str">
         <f t="array" ref="G16">_xlfn.IFS(AND(D16="", E16=""), "Have not started", OR(D16="", E16=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A17" s="15"/>
-      <c r="B17" s="9" t="s">
+    <row r="17" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="11">
+        <v>3</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4" t="s">
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="11" t="str">
+      <c r="G17" s="8" t="str">
         <f t="array" ref="G17">_xlfn.IFS(AND(D17="", E17=""), "Have not started", OR(D17="", E17=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A18" s="15"/>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="11">
+        <v>3</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="4" t="s">
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="11" t="str">
+      <c r="G18" s="8" t="str">
         <f t="array" ref="G18">_xlfn.IFS(AND(D18="", E18=""), "Have not started", OR(D18="", E18=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A19" s="16"/>
-      <c r="B19" s="9" t="s">
+    <row r="19" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="11">
+        <v>3</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="4" t="s">
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="G19" s="11" t="str">
+      <c r="G19" s="8" t="str">
         <f t="array" ref="G19">_xlfn.IFS(AND(D19="", E19=""), "Have not started", OR(D19="", E19=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A20" s="14">
+    <row r="20" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="11">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="4" t="s">
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G20" s="11" t="str">
+      <c r="G20" s="8" t="str">
         <f t="array" ref="G20">_xlfn.IFS(AND(D20="", E20=""), "Have not started", OR(D20="", E20=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A21" s="15"/>
-      <c r="B21" s="9" t="s">
+    <row r="21" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="11">
+        <v>4</v>
+      </c>
+      <c r="B21" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="4" t="s">
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="11" t="str">
+      <c r="G21" s="8" t="str">
         <f t="array" ref="G21">_xlfn.IFS(AND(D21="", E21=""), "Have not started", OR(D21="", E21=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A22" s="15"/>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="11">
+        <v>4</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4" t="s">
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G22" s="11" t="str">
+      <c r="G22" s="8" t="str">
         <f t="array" ref="G22">_xlfn.IFS(AND(D22="", E22=""), "Have not started", OR(D22="", E22=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A23" s="15"/>
-      <c r="B23" s="9" t="s">
+    <row r="23" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="11">
+        <v>4</v>
+      </c>
+      <c r="B23" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="4" t="s">
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G23" s="11" t="str">
+      <c r="G23" s="8" t="str">
         <f t="array" ref="G23">_xlfn.IFS(AND(D23="", E23=""), "Have not started", OR(D23="", E23=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A24" s="15"/>
-      <c r="B24" s="9" t="s">
+    <row r="24" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="11">
+        <v>4</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="4" t="s">
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="11" t="str">
+      <c r="G24" s="8" t="str">
         <f t="array" ref="G24">_xlfn.IFS(AND(D24="", E24=""), "Have not started", OR(D24="", E24=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A25" s="16"/>
-      <c r="B25" s="9" t="s">
+    <row r="25" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="11">
+        <v>4</v>
+      </c>
+      <c r="B25" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4" t="s">
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="11" t="str">
+      <c r="G25" s="8" t="str">
         <f t="array" ref="G25">_xlfn.IFS(AND(D25="", E25=""), "Have not started", OR(D25="", E25=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A26" s="14">
+    <row r="26" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="11">
         <v>5</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="4" t="s">
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G26" s="11" t="str">
+      <c r="G26" s="8" t="str">
         <f t="array" ref="G26">_xlfn.IFS(AND(D26="", E26=""), "Have not started", OR(D26="", E26=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A27" s="15"/>
-      <c r="B27" s="9" t="s">
+    <row r="27" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="11">
+        <v>5</v>
+      </c>
+      <c r="B27" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="4" t="s">
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="11" t="str">
+      <c r="G27" s="8" t="str">
         <f t="array" ref="G27">_xlfn.IFS(AND(D27="", E27=""), "Have not started", OR(D27="", E27=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A28" s="15"/>
-      <c r="B28" s="9" t="s">
+    <row r="28" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="11">
+        <v>5</v>
+      </c>
+      <c r="B28" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="4" t="s">
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="11" t="str">
+      <c r="G28" s="8" t="str">
         <f t="array" ref="G28">_xlfn.IFS(AND(D28="", E28=""), "Have not started", OR(D28="", E28=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A29" s="15"/>
-      <c r="B29" s="9" t="s">
+    <row r="29" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="11">
+        <v>5</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="4" t="s">
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="G29" s="11" t="str">
+      <c r="G29" s="8" t="str">
         <f t="array" ref="G29">_xlfn.IFS(AND(D29="", E29=""), "Have not started", OR(D29="", E29=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A30" s="15"/>
-      <c r="B30" s="9" t="s">
+    <row r="30" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="11">
+        <v>5</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="4" t="s">
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="11" t="str">
+      <c r="G30" s="8" t="str">
         <f t="array" ref="G30">_xlfn.IFS(AND(D30="", E30=""), "Have not started", OR(D30="", E30=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A31" s="16"/>
-      <c r="B31" s="9" t="s">
+    <row r="31" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="11">
+        <v>5</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="4" t="s">
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="11" t="str">
+      <c r="G31" s="8" t="str">
         <f t="array" ref="G31">_xlfn.IFS(AND(D31="", E31=""), "Have not started", OR(D31="", E31=""), "...", TRUE, "Finished")</f>
         <v>Have not started</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A26:A31"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A2:A7"/>
-    <mergeCell ref="A14:A19"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
@@ -1233,34 +1250,34 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1467,34 +1484,34 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="10" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdulaziz\Desktop\Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58AE2A21-EF30-45A3-8957-18ED33DA849E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA1C6FE-C479-4F4A-B895-4C26F16A9C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,14 +728,18 @@
       <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
+      <c r="D6" s="8">
+        <v>8</v>
+      </c>
+      <c r="E6" s="8">
+        <v>11</v>
+      </c>
       <c r="F6" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G6" s="8" t="str">
         <f t="array" ref="G6">_xlfn.IFS(AND(D6="", E6=""), "Have not started", OR(D6="", E6=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
+        <v>Finished</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdulaziz\Desktop\Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DA1C6FE-C479-4F4A-B895-4C26F16A9C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FD8E29-B8AB-481C-9ECE-17F3B6560735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -752,14 +752,18 @@
       <c r="C7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
+      <c r="D7" s="8">
+        <v>4</v>
+      </c>
+      <c r="E7" s="8">
+        <v>3</v>
+      </c>
       <c r="F7" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G7" s="8" t="str">
         <f t="array" ref="G7">_xlfn.IFS(AND(D7="", E7=""), "Have not started", OR(D7="", E7=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
+        <v>Finished</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">

--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdulaziz\Desktop\Tournament\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\My_Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97FD8E29-B8AB-481C-9ECE-17F3B6560735}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5076E546-A298-471D-AD5A-E5DB7C33F35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matches" sheetId="1" r:id="rId1"/>
@@ -588,18 +588,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="8.7265625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="20.453125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" style="5" customWidth="1"/>
+    <col min="4" max="5" width="8.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" style="9" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -622,7 +622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -646,7 +646,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -670,7 +670,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -694,7 +694,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -718,7 +718,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -742,7 +742,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -766,7 +766,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>2</v>
       </c>
@@ -776,17 +776,21 @@
       <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
+      <c r="D8" s="8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="8">
+        <v>7</v>
+      </c>
       <c r="F8" s="8" t="s">
         <v>14</v>
       </c>
       <c r="G8" s="8" t="str">
         <f t="array" ref="G8">_xlfn.IFS(AND(D8="", E8=""), "Have not started", OR(D8="", E8=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>Finished</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -806,7 +810,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>2</v>
       </c>
@@ -826,7 +830,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11">
         <v>2</v>
       </c>
@@ -846,7 +850,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
         <v>2</v>
       </c>
@@ -866,7 +870,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11">
         <v>2</v>
       </c>
@@ -886,7 +890,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
         <v>3</v>
       </c>
@@ -906,7 +910,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11">
         <v>3</v>
       </c>
@@ -926,7 +930,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
         <v>3</v>
       </c>
@@ -946,7 +950,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11">
         <v>3</v>
       </c>
@@ -966,7 +970,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
         <v>3</v>
       </c>
@@ -986,7 +990,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11">
         <v>3</v>
       </c>
@@ -1006,7 +1010,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
         <v>4</v>
       </c>
@@ -1026,7 +1030,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11">
         <v>4</v>
       </c>
@@ -1046,7 +1050,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>4</v>
       </c>
@@ -1066,7 +1070,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11">
         <v>4</v>
       </c>
@@ -1086,7 +1090,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>4</v>
       </c>
@@ -1106,7 +1110,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -1126,7 +1130,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -1146,7 +1150,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="11">
         <v>5</v>
       </c>
@@ -1166,7 +1170,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
         <v>5</v>
       </c>
@@ -1186,7 +1190,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11">
         <v>5</v>
       </c>
@@ -1206,7 +1210,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
         <v>5</v>
       </c>
@@ -1226,7 +1230,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11">
         <v>5</v>
       </c>
@@ -1255,9 +1259,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:J8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
@@ -1289,7 +1293,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1321,7 +1325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1353,7 +1357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1385,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1417,7 +1421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1449,7 +1453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1489,9 +1493,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:J8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
@@ -1523,7 +1527,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1555,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1587,7 +1591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1619,7 +1623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1651,7 +1655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1683,7 +1687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>6</v>
       </c>

--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\My_Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5076E546-A298-471D-AD5A-E5DB7C33F35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FA96E1-57E0-41D8-9DCB-C248455F573C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -800,14 +800,18 @@
       <c r="C9" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
+      <c r="D9" s="8">
+        <v>6</v>
+      </c>
+      <c r="E9" s="8">
+        <v>6</v>
+      </c>
       <c r="F9" s="8" t="s">
         <v>16</v>
       </c>
       <c r="G9" s="8" t="str">
         <f t="array" ref="G9">_xlfn.IFS(AND(D9="", E9=""), "Have not started", OR(D9="", E9=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
+        <v>Finished</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">

--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\My_Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11FA96E1-57E0-41D8-9DCB-C248455F573C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF93773E-4FA2-477E-AD20-4D292024D7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -824,14 +824,18 @@
       <c r="C10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
+      <c r="D10" s="8">
+        <v>7</v>
+      </c>
+      <c r="E10" s="8">
+        <v>7</v>
+      </c>
       <c r="F10" s="8" t="s">
         <v>18</v>
       </c>
       <c r="G10" s="8" t="str">
         <f t="array" ref="G10">_xlfn.IFS(AND(D10="", E10=""), "Have not started", OR(D10="", E10=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
+        <v>Finished</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">

--- a/Tournament_6_Teams.xlsx
+++ b/Tournament_6_Teams.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\My_Tournament\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abdulaziz\Desktop\Tournament\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF93773E-4FA2-477E-AD20-4D292024D7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711198C2-7248-445D-B936-0F23C5DCDBEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Matches" sheetId="1" r:id="rId1"/>
@@ -588,18 +588,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" style="5" customWidth="1"/>
-    <col min="4" max="5" width="8.7109375" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="20.42578125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="10.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.7265625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" style="5" customWidth="1"/>
+    <col min="4" max="5" width="8.7265625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.453125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="20.453125" style="9" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -622,7 +622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11">
         <v>1</v>
       </c>
@@ -646,7 +646,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -670,7 +670,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="11">
         <v>1</v>
       </c>
@@ -694,7 +694,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="11">
         <v>1</v>
       </c>
@@ -718,7 +718,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -742,7 +742,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -766,7 +766,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>2</v>
       </c>
@@ -790,7 +790,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>2</v>
       </c>
@@ -814,7 +814,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>2</v>
       </c>
@@ -838,7 +838,7 @@
         <v>Finished</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="11">
         <v>2</v>
       </c>
@@ -848,17 +848,21 @@
       <c r="C11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
+      <c r="D11" s="8">
+        <v>5</v>
+      </c>
+      <c r="E11" s="8">
+        <v>7</v>
+      </c>
       <c r="F11" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G11" s="8" t="str">
         <f t="array" ref="G11">_xlfn.IFS(AND(D11="", E11=""), "Have not started", OR(D11="", E11=""), "...", TRUE, "Finished")</f>
-        <v>Have not started</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+        <v>Finished</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="11">
         <v>2</v>
       </c>
@@ -878,7 +882,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>2</v>
       </c>
@@ -898,7 +902,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>3</v>
       </c>
@@ -918,7 +922,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>3</v>
       </c>
@@ -938,7 +942,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11">
         <v>3</v>
       </c>
@@ -958,7 +962,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="11">
         <v>3</v>
       </c>
@@ -978,7 +982,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="11">
         <v>3</v>
       </c>
@@ -998,7 +1002,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="11">
         <v>3</v>
       </c>
@@ -1018,7 +1022,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11">
         <v>4</v>
       </c>
@@ -1038,7 +1042,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="11">
         <v>4</v>
       </c>
@@ -1058,7 +1062,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="11">
         <v>4</v>
       </c>
@@ -1078,7 +1082,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="11">
         <v>4</v>
       </c>
@@ -1098,7 +1102,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="11">
         <v>4</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="11">
         <v>4</v>
       </c>
@@ -1138,7 +1142,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="11">
         <v>5</v>
       </c>
@@ -1158,7 +1162,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="11">
         <v>5</v>
       </c>
@@ -1178,7 +1182,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="11">
         <v>5</v>
       </c>
@@ -1198,7 +1202,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="11">
         <v>5</v>
       </c>
@@ -1218,7 +1222,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="11">
         <v>5</v>
       </c>
@@ -1238,7 +1242,7 @@
         <v>Have not started</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="11">
         <v>5</v>
       </c>
@@ -1267,9 +1271,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:J8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
@@ -1301,7 +1305,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1333,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1365,7 +1369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1397,7 +1401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1429,7 +1433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1461,7 +1465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1501,9 +1505,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:J8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>21</v>
       </c>
@@ -1535,7 +1539,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1567,7 +1571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1599,7 +1603,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1631,7 +1635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1663,7 +1667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1695,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
